--- a/product-definitions/spreadsheet/stability-indices.xlsx
+++ b/product-definitions/spreadsheet/stability-indices.xlsx
@@ -308,7 +308,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -334,14 +334,9 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -359,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -380,17 +375,16 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -399,17 +393,14 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1781,7 +1772,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
@@ -1789,23 +1780,23 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -1813,7 +1804,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1821,42 +1812,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1866,7 +1857,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -1874,23 +1865,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -1898,7 +1889,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -1906,2084 +1897,2089 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="8" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="8" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="8" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="8" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="8" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="8" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="8" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="8" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="8" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="8" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="B32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="8" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="8" t="s">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="B34" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="8" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="B35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="8" t="s">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="s">
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="8" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="8" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="8" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="8" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="B42" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="8" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="B43" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="8" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="8" t="s">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="B45" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="8" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="B46" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="8" t="s">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="8" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="8" t="s">
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="8" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="B51" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="8" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="B52" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="8" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="B53" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="8" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="B54" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="8" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="B55" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="8" t="s">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="B56" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="8" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="B57" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="8" t="s">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="B58" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="8" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="B59" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="8" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="B60" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="s">
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="8" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="8" t="s">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="8" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="B65" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="8" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="B66" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="8" t="s">
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="B67" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="8" t="s">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="B68" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="8" t="s">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="B69" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="8" t="s">
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="B70" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="8" t="s">
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="B71" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="8" t="s">
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="B72" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="11" t="s">
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="12"/>
-      <c r="B75" s="12" t="s">
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D75" s="12"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="12"/>
-      <c r="B76" s="12" t="s">
+      <c r="D75" s="11"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D76" s="12"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="12"/>
-      <c r="B77" s="12" t="s">
+      <c r="D76" s="11"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="13">
+      <c r="C77" s="12">
         <v>1.0</v>
       </c>
-      <c r="D77" s="12"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12" t="s">
+      <c r="D77" s="11"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="12"/>
-      <c r="B79" s="12" t="s">
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D79" s="12"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="12"/>
-      <c r="B80" s="12" t="s">
+      <c r="D79" s="11"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D80" s="12"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="12"/>
-      <c r="B81" s="15" t="s">
+      <c r="D80" s="11"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="11"/>
+      <c r="B81" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D81" s="12"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="s">
+      <c r="D81" s="11"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="12"/>
-      <c r="B84" s="12" t="s">
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D84" s="12"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="12"/>
-      <c r="B85" s="12" t="s">
+      <c r="D84" s="11"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="11"/>
+      <c r="B85" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D85" s="12"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="12"/>
-      <c r="B86" s="12" t="s">
+      <c r="D85" s="11"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="11"/>
+      <c r="B86" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="13">
+      <c r="C86" s="12">
         <v>1.0</v>
       </c>
-      <c r="D86" s="12"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="12"/>
-      <c r="B87" s="12" t="s">
+      <c r="D86" s="11"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="11"/>
+      <c r="B87" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="12"/>
-      <c r="B88" s="12" t="s">
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="11"/>
+      <c r="B88" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D88" s="12"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="12"/>
-      <c r="B89" s="12" t="s">
+      <c r="D88" s="11"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="11"/>
+      <c r="B89" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D89" s="12"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="12"/>
-      <c r="B90" s="15" t="s">
+      <c r="D89" s="11"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="11"/>
+      <c r="B90" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D90" s="12"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="12"/>
-      <c r="B91" s="12"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="12"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="11" t="s">
+      <c r="D90" s="11"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="12"/>
-      <c r="B93" s="12" t="s">
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="11"/>
+      <c r="B93" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="12"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12"/>
-      <c r="B94" s="12" t="s">
+      <c r="D93" s="11"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D94" s="12"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12" t="s">
+      <c r="D94" s="11"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="11"/>
+      <c r="B95" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C95" s="13">
+      <c r="C95" s="12">
         <v>1.0</v>
       </c>
-      <c r="D95" s="12"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="12"/>
-      <c r="B96" s="12" t="s">
+      <c r="D95" s="11"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="11"/>
+      <c r="B96" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="12"/>
-      <c r="D96" s="12"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="12"/>
-      <c r="B97" s="12" t="s">
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="11"/>
+      <c r="B97" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D97" s="12"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="12"/>
-      <c r="B98" s="12" t="s">
+      <c r="D97" s="11"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D98" s="12"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="12"/>
-      <c r="B99" s="15" t="s">
+      <c r="D98" s="11"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="11"/>
+      <c r="B99" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="C99" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D99" s="12"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="12" t="s">
+      <c r="D99" s="11"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="12"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="12"/>
-      <c r="B102" s="12" t="s">
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D102" s="12"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="12"/>
-      <c r="B103" s="12" t="s">
+      <c r="D102" s="11"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="11"/>
+      <c r="B103" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D103" s="12"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="12"/>
-      <c r="B104" s="12" t="s">
+      <c r="D103" s="11"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C104" s="17">
+      <c r="C104" s="16">
         <v>1.0</v>
       </c>
-      <c r="D104" s="12"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="12"/>
-      <c r="B105" s="12" t="s">
+      <c r="D104" s="11"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="11"/>
+      <c r="B105" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C105" s="17"/>
-      <c r="D105" s="12"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12" t="s">
+      <c r="C105" s="16"/>
+      <c r="D105" s="11"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="11"/>
+      <c r="B106" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D106" s="12"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="12"/>
-      <c r="B107" s="12" t="s">
+      <c r="D106" s="11"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="11"/>
+      <c r="B107" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C107" s="14" t="s">
+      <c r="C107" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D107" s="12"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="12"/>
-      <c r="B108" s="15" t="s">
+      <c r="D107" s="11"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="11"/>
+      <c r="B108" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="C108" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D108" s="12"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="17"/>
-      <c r="D109" s="12"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="11" t="s">
+      <c r="D108" s="11"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="11"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="11"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="12"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="12"/>
-      <c r="B111" s="12" t="s">
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="11"/>
+      <c r="B111" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="12" t="s">
+      <c r="C111" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D111" s="12"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="12"/>
-      <c r="B112" s="12" t="s">
+      <c r="D111" s="11"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="11"/>
+      <c r="B112" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D112" s="12"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="12"/>
-      <c r="B113" s="12" t="s">
+      <c r="D112" s="11"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="11"/>
+      <c r="B113" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C113" s="17">
+      <c r="C113" s="16">
         <v>1.0</v>
       </c>
-      <c r="D113" s="12"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="12"/>
-      <c r="B114" s="12" t="s">
+      <c r="D113" s="11"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="11"/>
+      <c r="B114" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C114" s="17"/>
-      <c r="D114" s="12"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="12"/>
-      <c r="B115" s="12" t="s">
+      <c r="C114" s="16"/>
+      <c r="D114" s="11"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="11"/>
+      <c r="B115" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D115" s="12"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="12"/>
-      <c r="B116" s="12" t="s">
+      <c r="D115" s="11"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="11"/>
+      <c r="B116" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C116" s="14" t="s">
+      <c r="C116" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D116" s="12"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="12"/>
-      <c r="B117" s="15" t="s">
+      <c r="D116" s="11"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="11"/>
+      <c r="B117" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C117" s="16" t="s">
+      <c r="C117" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D117" s="12"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="12"/>
-      <c r="B118" s="12"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="12"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="11" t="s">
+      <c r="D117" s="11"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="11"/>
+      <c r="B118" s="11"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="12"/>
-      <c r="B120" s="12" t="s">
+      <c r="B119" s="11"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="11"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="11"/>
+      <c r="B120" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D120" s="12"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12" t="s">
+      <c r="D120" s="11"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="11"/>
+      <c r="B121" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D121" s="12"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="12"/>
-      <c r="B122" s="12" t="s">
+      <c r="D121" s="11"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="11"/>
+      <c r="B122" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C122" s="17">
+      <c r="C122" s="16">
         <v>1.0</v>
       </c>
-      <c r="D122" s="12"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="12"/>
-      <c r="B123" s="12" t="s">
+      <c r="D122" s="11"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="11"/>
+      <c r="B123" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C123" s="17"/>
-      <c r="D123" s="12"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="12"/>
-      <c r="B124" s="12" t="s">
+      <c r="C123" s="16"/>
+      <c r="D123" s="11"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="11"/>
+      <c r="B124" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D124" s="12"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="12"/>
-      <c r="B125" s="12" t="s">
+      <c r="D124" s="11"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="11"/>
+      <c r="B125" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D125" s="12"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="12"/>
-      <c r="B126" s="15" t="s">
+      <c r="D125" s="11"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="11"/>
+      <c r="B126" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C126" s="16" t="s">
+      <c r="C126" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D126" s="12"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="12"/>
-      <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="11" t="s">
+      <c r="D126" s="11"/>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="11"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B128" s="12"/>
-      <c r="C128" s="12"/>
-      <c r="D128" s="12"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="12"/>
-      <c r="B129" s="12" t="s">
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="11"/>
+      <c r="B129" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C129" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D129" s="12"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="12"/>
-      <c r="B130" s="12" t="s">
+      <c r="D129" s="11"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="11"/>
+      <c r="B130" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D130" s="12"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12" t="s">
+      <c r="D130" s="11"/>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="11"/>
+      <c r="B131" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C131" s="17">
+      <c r="C131" s="16">
         <v>1.0</v>
       </c>
-      <c r="D131" s="12"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="12"/>
-      <c r="B132" s="12" t="s">
+      <c r="D131" s="11"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="11"/>
+      <c r="B132" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C132" s="17"/>
-      <c r="D132" s="12"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="12"/>
-      <c r="B133" s="12" t="s">
+      <c r="C132" s="16"/>
+      <c r="D132" s="11"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="11"/>
+      <c r="B133" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D133" s="12"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12" t="s">
+      <c r="D133" s="11"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="11"/>
+      <c r="B134" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C134" s="14" t="s">
+      <c r="C134" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D134" s="12"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="12"/>
-      <c r="B135" s="15" t="s">
+      <c r="D134" s="11"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="11"/>
+      <c r="B135" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C135" s="16" t="s">
+      <c r="C135" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D135" s="12"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="12"/>
-      <c r="B136" s="12"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="s">
+      <c r="D135" s="11"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="11"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B137" s="12"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="12"/>
-      <c r="B138" s="12" t="s">
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="11"/>
+      <c r="B138" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D138" s="12"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="12"/>
-      <c r="B139" s="12" t="s">
+      <c r="D138" s="11"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="11"/>
+      <c r="B139" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D139" s="12"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="12"/>
-      <c r="B140" s="12" t="s">
+      <c r="D139" s="11"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="11"/>
+      <c r="B140" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C140" s="17">
+      <c r="C140" s="16">
         <v>1.0</v>
       </c>
-      <c r="D140" s="12"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="12"/>
-      <c r="B141" s="12" t="s">
+      <c r="D140" s="11"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="11"/>
+      <c r="B141" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C141" s="17"/>
-      <c r="D141" s="12"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="12"/>
-      <c r="B142" s="12" t="s">
+      <c r="C141" s="16"/>
+      <c r="D141" s="11"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="11"/>
+      <c r="B142" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C142" s="11" t="s">
+      <c r="C142" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D142" s="12"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="12"/>
-      <c r="B143" s="12" t="s">
+      <c r="D142" s="11"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="11"/>
+      <c r="B143" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C143" s="14" t="s">
+      <c r="C143" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D143" s="12"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="12"/>
-      <c r="B144" s="15" t="s">
+      <c r="D143" s="11"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="11"/>
+      <c r="B144" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C144" s="16" t="s">
+      <c r="C144" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D144" s="12"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="12"/>
-      <c r="B145" s="12"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="12"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="11" t="s">
+      <c r="D144" s="11"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="11"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B146" s="12"/>
-      <c r="C146" s="12"/>
-      <c r="D146" s="12"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="12"/>
-      <c r="B147" s="12" t="s">
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="11"/>
+      <c r="B147" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C147" s="12" t="s">
+      <c r="C147" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D147" s="12"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="12"/>
-      <c r="B148" s="12" t="s">
+      <c r="D147" s="11"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="11"/>
+      <c r="B148" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C148" s="12" t="s">
+      <c r="C148" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D148" s="12"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="12"/>
-      <c r="B149" s="12" t="s">
+      <c r="D148" s="11"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="11"/>
+      <c r="B149" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C149" s="17">
+      <c r="C149" s="16">
         <v>1.0</v>
       </c>
-      <c r="D149" s="12"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="12"/>
-      <c r="B150" s="12" t="s">
+      <c r="D149" s="11"/>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="11"/>
+      <c r="B150" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C150" s="17"/>
-      <c r="D150" s="12"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="12"/>
-      <c r="B151" s="12" t="s">
+      <c r="C150" s="16"/>
+      <c r="D150" s="11"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="11"/>
+      <c r="B151" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D151" s="12"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="12"/>
-      <c r="B152" s="12" t="s">
+      <c r="D151" s="11"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="11"/>
+      <c r="B152" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C152" s="14" t="s">
+      <c r="C152" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D152" s="12"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="12"/>
-      <c r="B153" s="15" t="s">
+      <c r="D152" s="11"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="11"/>
+      <c r="B153" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C153" s="16" t="s">
+      <c r="C153" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D153" s="12"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="12"/>
-      <c r="B154" s="12"/>
-      <c r="C154" s="12"/>
-      <c r="D154" s="12"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="11" t="s">
+      <c r="D153" s="11"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="11"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B155" s="12"/>
-      <c r="C155" s="12"/>
-      <c r="D155" s="12"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="12"/>
-      <c r="B156" s="12" t="s">
+      <c r="B155" s="11"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="11"/>
+      <c r="B156" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D156" s="12"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="12"/>
-      <c r="B157" s="12" t="s">
+      <c r="D156" s="11"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="11"/>
+      <c r="B157" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C157" s="12" t="s">
+      <c r="C157" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D157" s="12"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="12"/>
-      <c r="B158" s="12" t="s">
+      <c r="D157" s="11"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="11"/>
+      <c r="B158" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C158" s="17">
+      <c r="C158" s="16">
         <v>1.0</v>
       </c>
-      <c r="D158" s="12"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="12"/>
-      <c r="B159" s="12" t="s">
+      <c r="D158" s="11"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="11"/>
+      <c r="B159" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C159" s="17"/>
-      <c r="D159" s="12"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="12"/>
-      <c r="B160" s="12" t="s">
+      <c r="C159" s="16"/>
+      <c r="D159" s="11"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="11"/>
+      <c r="B160" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C160" s="11" t="s">
+      <c r="C160" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D160" s="12"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="12"/>
-      <c r="B161" s="12" t="s">
+      <c r="D160" s="11"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="11"/>
+      <c r="B161" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C161" s="14" t="s">
+      <c r="C161" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D161" s="12"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="12"/>
-      <c r="B162" s="15" t="s">
+      <c r="D161" s="11"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="11"/>
+      <c r="B162" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C162" s="16" t="s">
+      <c r="C162" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D162" s="12"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="12"/>
-      <c r="B163" s="12"/>
-      <c r="C163" s="12"/>
-      <c r="D163" s="12"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="11" t="s">
+      <c r="D162" s="11"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="11"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B164" s="12"/>
-      <c r="C164" s="12"/>
-      <c r="D164" s="12"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="12"/>
-      <c r="B165" s="12" t="s">
+      <c r="B164" s="11"/>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="11"/>
+      <c r="B165" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C165" s="12" t="s">
+      <c r="C165" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D165" s="12"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="12"/>
-      <c r="B166" s="12" t="s">
+      <c r="D165" s="11"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="11"/>
+      <c r="B166" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C166" s="12" t="s">
+      <c r="C166" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D166" s="12"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="12"/>
-      <c r="B167" s="12" t="s">
+      <c r="D166" s="11"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="11"/>
+      <c r="B167" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C167" s="17">
+      <c r="C167" s="16">
         <v>1.0</v>
       </c>
-      <c r="D167" s="12"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="12"/>
-      <c r="B168" s="12" t="s">
+      <c r="D167" s="11"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="11"/>
+      <c r="B168" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C168" s="17"/>
-      <c r="D168" s="12"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="12"/>
-      <c r="B169" s="12" t="s">
+      <c r="C168" s="16"/>
+      <c r="D168" s="11"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="11"/>
+      <c r="B169" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C169" s="11" t="s">
+      <c r="C169" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D169" s="12"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="12"/>
-      <c r="B170" s="12" t="s">
+      <c r="D169" s="11"/>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="11"/>
+      <c r="B170" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C170" s="14" t="s">
+      <c r="C170" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D170" s="12"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="12"/>
-      <c r="B171" s="15" t="s">
+      <c r="D170" s="11"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="11"/>
+      <c r="B171" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C171" s="16" t="s">
+      <c r="C171" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D171" s="12"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="12"/>
-      <c r="B172" s="12"/>
-      <c r="C172" s="12"/>
-      <c r="D172" s="12"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="11" t="s">
+      <c r="D171" s="11"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="11"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="11"/>
+      <c r="D172" s="11"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B173" s="12"/>
-      <c r="C173" s="12"/>
-      <c r="D173" s="12"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="12"/>
-      <c r="B174" s="12" t="s">
+      <c r="B173" s="11"/>
+      <c r="C173" s="11"/>
+      <c r="D173" s="11"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="11"/>
+      <c r="B174" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D174" s="12"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="12"/>
-      <c r="B175" s="12" t="s">
+      <c r="D174" s="11"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="11"/>
+      <c r="B175" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C175" s="12" t="s">
+      <c r="C175" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D175" s="12"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="12"/>
-      <c r="B176" s="12" t="s">
+      <c r="D175" s="11"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="11"/>
+      <c r="B176" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C176" s="17">
+      <c r="C176" s="16">
         <v>1.0</v>
       </c>
-      <c r="D176" s="12"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="12"/>
-      <c r="B177" s="12" t="s">
+      <c r="D176" s="11"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="11"/>
+      <c r="B177" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C177" s="17"/>
-      <c r="D177" s="12"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="12"/>
-      <c r="B178" s="12" t="s">
+      <c r="C177" s="16"/>
+      <c r="D177" s="11"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="11"/>
+      <c r="B178" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C178" s="11" t="s">
+      <c r="C178" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D178" s="12"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="12"/>
-      <c r="B179" s="12" t="s">
+      <c r="D178" s="11"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="11"/>
+      <c r="B179" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C179" s="14" t="s">
+      <c r="C179" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D179" s="12"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="12"/>
-      <c r="B180" s="15" t="s">
+      <c r="D179" s="11"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
+      <c r="A180" s="11"/>
+      <c r="B180" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C180" s="16" t="s">
+      <c r="C180" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D180" s="12"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="12"/>
-      <c r="B181" s="12"/>
-      <c r="C181" s="12"/>
-      <c r="D181" s="12"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="11" t="s">
+      <c r="D180" s="11"/>
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
+      <c r="A181" s="11"/>
+      <c r="B181" s="11"/>
+      <c r="C181" s="11"/>
+      <c r="D181" s="11"/>
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
+      <c r="A182" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B182" s="12"/>
-      <c r="C182" s="12"/>
-      <c r="D182" s="12"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="12"/>
-      <c r="B183" s="12" t="s">
+      <c r="B182" s="11"/>
+      <c r="C182" s="11"/>
+      <c r="D182" s="11"/>
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
+      <c r="A183" s="11"/>
+      <c r="B183" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C183" s="12" t="s">
+      <c r="C183" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D183" s="12"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="12"/>
-      <c r="B184" s="12" t="s">
+      <c r="D183" s="11"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="11"/>
+      <c r="B184" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C184" s="12" t="s">
+      <c r="C184" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D184" s="12"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="12"/>
-      <c r="B185" s="12" t="s">
+      <c r="D184" s="11"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
+      <c r="A185" s="11"/>
+      <c r="B185" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C185" s="17">
+      <c r="C185" s="16">
         <v>1.0</v>
       </c>
-      <c r="D185" s="12"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="12"/>
-      <c r="B186" s="12" t="s">
+      <c r="D185" s="11"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="11"/>
+      <c r="B186" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C186" s="17"/>
-      <c r="D186" s="12"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="12"/>
-      <c r="B187" s="12" t="s">
+      <c r="C186" s="16"/>
+      <c r="D186" s="11"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
+      <c r="A187" s="11"/>
+      <c r="B187" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C187" s="11" t="s">
+      <c r="C187" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D187" s="12"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="12"/>
-      <c r="B188" s="12" t="s">
+      <c r="D187" s="11"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
+      <c r="A188" s="11"/>
+      <c r="B188" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C188" s="14" t="s">
+      <c r="C188" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D188" s="12"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="12"/>
-      <c r="B189" s="15" t="s">
+      <c r="D188" s="11"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="11"/>
+      <c r="B189" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C189" s="16" t="s">
+      <c r="C189" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D189" s="12"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="12"/>
-      <c r="B190" s="12"/>
-      <c r="C190" s="12"/>
-      <c r="D190" s="12"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="11" t="s">
+      <c r="D189" s="11"/>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="11"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="11"/>
+      <c r="D190" s="11"/>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B191" s="12"/>
-      <c r="C191" s="12"/>
-      <c r="D191" s="12"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="12"/>
-      <c r="B192" s="12" t="s">
+      <c r="B191" s="11"/>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11"/>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="11"/>
+      <c r="B192" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C192" s="12" t="s">
+      <c r="C192" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D192" s="12"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="12"/>
-      <c r="B193" s="12" t="s">
+      <c r="D192" s="11"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="11"/>
+      <c r="B193" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C193" s="12" t="s">
+      <c r="C193" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D193" s="12"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="12"/>
-      <c r="B194" s="12" t="s">
+      <c r="D193" s="11"/>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="11"/>
+      <c r="B194" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C194" s="17">
+      <c r="C194" s="16">
         <v>1.0</v>
       </c>
-      <c r="D194" s="12"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="12"/>
-      <c r="B195" s="12" t="s">
+      <c r="D194" s="11"/>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="11"/>
+      <c r="B195" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C195" s="17"/>
-      <c r="D195" s="12"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="12"/>
-      <c r="B196" s="12" t="s">
+      <c r="C195" s="16"/>
+      <c r="D195" s="11"/>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="11"/>
+      <c r="B196" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C196" s="11" t="s">
+      <c r="C196" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D196" s="12"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="12"/>
-      <c r="B197" s="12" t="s">
+      <c r="D196" s="11"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="11"/>
+      <c r="B197" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C197" s="14" t="s">
+      <c r="C197" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D197" s="12"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="12"/>
-      <c r="B198" s="15" t="s">
+      <c r="D197" s="11"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="11"/>
+      <c r="B198" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C198" s="16" t="s">
+      <c r="C198" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D198" s="12"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="12"/>
-      <c r="B199" s="12"/>
-      <c r="C199" s="12"/>
-      <c r="D199" s="12"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="11" t="s">
+      <c r="D198" s="11"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="11"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="11"/>
+      <c r="D199" s="11"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B200" s="12"/>
-      <c r="C200" s="12"/>
-      <c r="D200" s="12"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="12"/>
-      <c r="B201" s="12" t="s">
+      <c r="B200" s="11"/>
+      <c r="C200" s="11"/>
+      <c r="D200" s="11"/>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="11"/>
+      <c r="B201" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C201" s="12" t="s">
+      <c r="C201" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D201" s="12"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="12"/>
-      <c r="B202" s="12" t="s">
+      <c r="D201" s="11"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="11"/>
+      <c r="B202" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C202" s="12" t="s">
+      <c r="C202" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D202" s="12"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="12"/>
-      <c r="B203" s="12" t="s">
+      <c r="D202" s="11"/>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="11"/>
+      <c r="B203" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C203" s="17">
+      <c r="C203" s="16">
         <v>1.0</v>
       </c>
-      <c r="D203" s="12"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="12"/>
-      <c r="B204" s="12" t="s">
+      <c r="D203" s="11"/>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="11"/>
+      <c r="B204" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C204" s="17"/>
-      <c r="D204" s="12"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="12"/>
-      <c r="B205" s="12" t="s">
+      <c r="C204" s="16"/>
+      <c r="D204" s="11"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="11"/>
+      <c r="B205" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C205" s="11" t="s">
+      <c r="C205" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D205" s="12"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="12"/>
-      <c r="B206" s="12" t="s">
+      <c r="D205" s="11"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="11"/>
+      <c r="B206" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C206" s="14" t="s">
+      <c r="C206" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D206" s="12"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="12"/>
-      <c r="B207" s="15" t="s">
+      <c r="D206" s="11"/>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="A207" s="11"/>
+      <c r="B207" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C207" s="16" t="s">
+      <c r="C207" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D207" s="12"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="12"/>
-      <c r="B208" s="12"/>
-      <c r="C208" s="12"/>
-      <c r="D208" s="12"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="11" t="s">
+      <c r="D207" s="11"/>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="A208" s="11"/>
+      <c r="B208" s="11"/>
+      <c r="C208" s="11"/>
+      <c r="D208" s="11"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="A209" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B209" s="12"/>
-      <c r="C209" s="12"/>
-      <c r="D209" s="12"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="12"/>
-      <c r="B210" s="12" t="s">
+      <c r="B209" s="11"/>
+      <c r="C209" s="11"/>
+      <c r="D209" s="11"/>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="A210" s="11"/>
+      <c r="B210" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C210" s="12" t="s">
+      <c r="C210" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D210" s="12"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="12"/>
-      <c r="B211" s="12" t="s">
+      <c r="D210" s="11"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="A211" s="11"/>
+      <c r="B211" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C211" s="12" t="s">
+      <c r="C211" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D211" s="12"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="12"/>
-      <c r="B212" s="12" t="s">
+      <c r="D211" s="11"/>
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
+      <c r="A212" s="11"/>
+      <c r="B212" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C212" s="17">
+      <c r="C212" s="16">
         <v>1.0</v>
       </c>
-      <c r="D212" s="12"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="12"/>
-      <c r="B213" s="12" t="s">
+      <c r="D212" s="11"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
+      <c r="A213" s="11"/>
+      <c r="B213" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C213" s="17"/>
-      <c r="D213" s="12"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="12"/>
-      <c r="B214" s="12" t="s">
+      <c r="C213" s="16"/>
+      <c r="D213" s="11"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
+      <c r="A214" s="11"/>
+      <c r="B214" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C214" s="11" t="s">
+      <c r="C214" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D214" s="12"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="12"/>
-      <c r="B215" s="12" t="s">
+      <c r="D214" s="11"/>
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
+      <c r="A215" s="11"/>
+      <c r="B215" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C215" s="14" t="s">
+      <c r="C215" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D215" s="12"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="12"/>
-      <c r="B216" s="15" t="s">
+      <c r="D215" s="11"/>
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
+      <c r="A216" s="11"/>
+      <c r="B216" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C216" s="16" t="s">
+      <c r="C216" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D216" s="12"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="12"/>
-      <c r="B217" s="12"/>
-      <c r="C217" s="12"/>
-      <c r="D217" s="12"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="11" t="s">
+      <c r="D216" s="11"/>
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
+      <c r="A217" s="11"/>
+      <c r="B217" s="11"/>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11"/>
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
+      <c r="A218" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B218" s="12"/>
-      <c r="C218" s="12"/>
-      <c r="D218" s="12"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="12"/>
-      <c r="B219" s="12" t="s">
+      <c r="B218" s="11"/>
+      <c r="C218" s="11"/>
+      <c r="D218" s="11"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
+      <c r="A219" s="11"/>
+      <c r="B219" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C219" s="12" t="s">
+      <c r="C219" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D219" s="12"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="12"/>
-      <c r="B220" s="12" t="s">
+      <c r="D219" s="11"/>
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
+      <c r="A220" s="11"/>
+      <c r="B220" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C220" s="12" t="s">
+      <c r="C220" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D220" s="12"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="12"/>
-      <c r="B221" s="12" t="s">
+      <c r="D220" s="11"/>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="A221" s="11"/>
+      <c r="B221" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C221" s="17">
+      <c r="C221" s="16">
         <v>1.0</v>
       </c>
-      <c r="D221" s="12"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="12"/>
-      <c r="B222" s="12" t="s">
+      <c r="D221" s="11"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="A222" s="11"/>
+      <c r="B222" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C222" s="17"/>
-      <c r="D222" s="12"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="12"/>
-      <c r="B223" s="12" t="s">
+      <c r="C222" s="16"/>
+      <c r="D222" s="11"/>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="A223" s="11"/>
+      <c r="B223" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C223" s="11" t="s">
+      <c r="C223" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D223" s="12"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="12"/>
-      <c r="B224" s="12" t="s">
+      <c r="D223" s="11"/>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="A224" s="11"/>
+      <c r="B224" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C224" s="14" t="s">
+      <c r="C224" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D224" s="12"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="12"/>
-      <c r="B225" s="15" t="s">
+      <c r="D224" s="11"/>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="A225" s="11"/>
+      <c r="B225" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C225" s="16" t="s">
+      <c r="C225" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D225" s="12"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="12"/>
-      <c r="B226" s="12"/>
-      <c r="C226" s="12"/>
-      <c r="D226" s="12"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="11" t="s">
+      <c r="D225" s="11"/>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="A226" s="11"/>
+      <c r="B226" s="11"/>
+      <c r="C226" s="11"/>
+      <c r="D226" s="11"/>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="A227" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B227" s="12"/>
-      <c r="C227" s="12"/>
-      <c r="D227" s="12"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="12"/>
-      <c r="B228" s="12" t="s">
+      <c r="B227" s="11"/>
+      <c r="C227" s="11"/>
+      <c r="D227" s="11"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="A228" s="11"/>
+      <c r="B228" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C228" s="12" t="s">
+      <c r="C228" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D228" s="12"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="12"/>
-      <c r="B229" s="12" t="s">
+      <c r="D228" s="11"/>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
+      <c r="A229" s="11"/>
+      <c r="B229" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C229" s="12" t="s">
+      <c r="C229" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D229" s="12"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="12"/>
-      <c r="B230" s="12" t="s">
+      <c r="D229" s="11"/>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="A230" s="11"/>
+      <c r="B230" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C230" s="17">
+      <c r="C230" s="16">
         <v>1.0</v>
       </c>
-      <c r="D230" s="12"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="12"/>
-      <c r="B231" s="12" t="s">
+      <c r="D230" s="11"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="A231" s="11"/>
+      <c r="B231" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C231" s="17"/>
-      <c r="D231" s="12"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="12"/>
-      <c r="B232" s="12" t="s">
+      <c r="C231" s="16"/>
+      <c r="D231" s="11"/>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="A232" s="11"/>
+      <c r="B232" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C232" s="11" t="s">
+      <c r="C232" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D232" s="12"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="12"/>
-      <c r="B233" s="12" t="s">
+      <c r="D232" s="11"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="A233" s="11"/>
+      <c r="B233" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C233" s="14" t="s">
+      <c r="C233" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D233" s="12"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="12"/>
-      <c r="B234" s="15" t="s">
+      <c r="D233" s="11"/>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="A234" s="11"/>
+      <c r="B234" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C234" s="16" t="s">
+      <c r="C234" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D234" s="12"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="12"/>
-      <c r="B235" s="12"/>
-      <c r="C235" s="12"/>
-      <c r="D235" s="12"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="11" t="s">
+      <c r="D234" s="11"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="A235" s="11"/>
+      <c r="B235" s="11"/>
+      <c r="C235" s="11"/>
+      <c r="D235" s="11"/>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="A236" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B236" s="12"/>
-      <c r="C236" s="12"/>
-      <c r="D236" s="12"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="12"/>
-      <c r="B237" s="12" t="s">
+      <c r="B236" s="11"/>
+      <c r="C236" s="11"/>
+      <c r="D236" s="11"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="A237" s="11"/>
+      <c r="B237" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C237" s="12" t="s">
+      <c r="C237" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D237" s="12"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="12"/>
-      <c r="B238" s="12" t="s">
+      <c r="D237" s="11"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
+      <c r="A238" s="11"/>
+      <c r="B238" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C238" s="12" t="s">
+      <c r="C238" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D238" s="12"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="12"/>
-      <c r="B239" s="12" t="s">
+      <c r="D238" s="11"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="A239" s="11"/>
+      <c r="B239" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C239" s="17">
+      <c r="C239" s="16">
         <v>1.0</v>
       </c>
-      <c r="D239" s="12"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="12"/>
-      <c r="B240" s="12" t="s">
+      <c r="D239" s="11"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="A240" s="11"/>
+      <c r="B240" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C240" s="17"/>
-      <c r="D240" s="12"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="12"/>
-      <c r="B241" s="12" t="s">
+      <c r="C240" s="16"/>
+      <c r="D240" s="11"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="A241" s="11"/>
+      <c r="B241" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C241" s="11" t="s">
+      <c r="C241" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D241" s="12"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="12"/>
-      <c r="B242" s="12" t="s">
+      <c r="D241" s="11"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="A242" s="11"/>
+      <c r="B242" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C242" s="14" t="s">
+      <c r="C242" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D242" s="12"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="12"/>
-      <c r="B243" s="15" t="s">
+      <c r="D242" s="11"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="A243" s="11"/>
+      <c r="B243" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C243" s="18" t="s">
+      <c r="C243" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D243" s="12"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="12"/>
-      <c r="B244" s="12"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="12"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="11" t="s">
+      <c r="D243" s="11"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="A244" s="11"/>
+      <c r="B244" s="11"/>
+      <c r="C244" s="11"/>
+      <c r="D244" s="11"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="A245" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B245" s="12"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="12"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="12"/>
-      <c r="B246" s="12" t="s">
+      <c r="B245" s="11"/>
+      <c r="C245" s="11"/>
+      <c r="D245" s="11"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="A246" s="11"/>
+      <c r="B246" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C246" s="12" t="s">
+      <c r="C246" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D246" s="12"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="12"/>
-      <c r="B247" s="12" t="s">
+      <c r="D246" s="11"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="A247" s="11"/>
+      <c r="B247" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C247" s="12" t="s">
+      <c r="C247" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D247" s="12"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="12"/>
-      <c r="B248" s="12" t="s">
+      <c r="D247" s="11"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="A248" s="11"/>
+      <c r="B248" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C248" s="17">
+      <c r="C248" s="16">
         <v>1.0</v>
       </c>
-      <c r="D248" s="12"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="12"/>
-      <c r="B249" s="12" t="s">
+      <c r="D248" s="11"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="A249" s="11"/>
+      <c r="B249" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C249" s="17"/>
-      <c r="D249" s="12"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="12"/>
-      <c r="B250" s="12" t="s">
+      <c r="C249" s="16"/>
+      <c r="D249" s="11"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="A250" s="11"/>
+      <c r="B250" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C250" s="11" t="s">
+      <c r="C250" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D250" s="12"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="12"/>
-      <c r="B251" s="12" t="s">
+      <c r="D250" s="11"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="A251" s="11"/>
+      <c r="B251" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C251" s="14" t="s">
+      <c r="C251" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D251" s="12"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="12"/>
-      <c r="B252" s="15" t="s">
+      <c r="D251" s="11"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="A252" s="11"/>
+      <c r="B252" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C252" s="18" t="s">
+      <c r="C252" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D252" s="12"/>
+      <c r="D252" s="11"/>
     </row>
     <row r="253" ht="12.0" customHeight="1">
-      <c r="A253" s="12"/>
-      <c r="B253" s="12"/>
-      <c r="C253" s="12"/>
-      <c r="D253" s="12"/>
+      <c r="A253" s="11"/>
+      <c r="B253" s="11"/>
+      <c r="C253" s="11"/>
+      <c r="D253" s="11"/>
     </row>
     <row r="254" ht="12.0" customHeight="1">
-      <c r="A254" s="12"/>
-      <c r="B254" s="12"/>
-      <c r="C254" s="12"/>
-      <c r="D254" s="12"/>
+      <c r="A254" s="11"/>
+      <c r="B254" s="11"/>
+      <c r="C254" s="11"/>
+      <c r="D254" s="11"/>
     </row>
     <row r="255" ht="12.0" customHeight="1">
-      <c r="A255" s="12"/>
-      <c r="B255" s="12"/>
-      <c r="C255" s="12"/>
-      <c r="D255" s="12"/>
+      <c r="A255" s="11"/>
+      <c r="B255" s="11"/>
+      <c r="C255" s="11"/>
+      <c r="D255" s="11"/>
     </row>
     <row r="256" ht="12.0" customHeight="1">
-      <c r="A256" s="12"/>
-      <c r="B256" s="12"/>
-      <c r="C256" s="12"/>
-      <c r="D256" s="12"/>
+      <c r="A256" s="11"/>
+      <c r="B256" s="11"/>
+      <c r="C256" s="11"/>
+      <c r="D256" s="11"/>
     </row>
     <row r="257" ht="12.0" customHeight="1">
-      <c r="A257" s="12"/>
-      <c r="B257" s="12"/>
-      <c r="C257" s="12"/>
-      <c r="D257" s="12"/>
+      <c r="A257" s="11"/>
+      <c r="B257" s="11"/>
+      <c r="C257" s="11"/>
+      <c r="D257" s="11"/>
     </row>
     <row r="258" ht="12.0" customHeight="1">
-      <c r="A258" s="12"/>
-      <c r="B258" s="12"/>
-      <c r="C258" s="12"/>
-      <c r="D258" s="12"/>
+      <c r="A258" s="11"/>
+      <c r="B258" s="11"/>
+      <c r="C258" s="11"/>
+      <c r="D258" s="11"/>
     </row>
     <row r="259" ht="12.0" customHeight="1">
-      <c r="A259" s="12"/>
-      <c r="B259" s="12"/>
-      <c r="C259" s="12"/>
-      <c r="D259" s="12"/>
+      <c r="A259" s="11"/>
+      <c r="B259" s="11"/>
+      <c r="C259" s="11"/>
+      <c r="D259" s="11"/>
     </row>
     <row r="260" ht="12.0" customHeight="1">
-      <c r="A260" s="12"/>
-      <c r="B260" s="12"/>
-      <c r="C260" s="12"/>
-      <c r="D260" s="12"/>
+      <c r="A260" s="11"/>
+      <c r="B260" s="11"/>
+      <c r="C260" s="11"/>
+      <c r="D260" s="11"/>
     </row>
     <row r="261" ht="12.0" customHeight="1">
-      <c r="A261" s="12"/>
-      <c r="B261" s="12"/>
-      <c r="C261" s="12"/>
-      <c r="D261" s="12"/>
+      <c r="A261" s="11"/>
+      <c r="B261" s="11"/>
+      <c r="C261" s="11"/>
+      <c r="D261" s="11"/>
     </row>
     <row r="262" ht="12.0" customHeight="1">
-      <c r="A262" s="12"/>
-      <c r="B262" s="12"/>
-      <c r="C262" s="12"/>
-      <c r="D262" s="12"/>
+      <c r="A262" s="11"/>
+      <c r="B262" s="11"/>
+      <c r="C262" s="11"/>
+      <c r="D262" s="11"/>
     </row>
     <row r="263" ht="12.0" customHeight="1">
-      <c r="A263" s="12"/>
-      <c r="B263" s="12"/>
-      <c r="C263" s="12"/>
-      <c r="D263" s="12"/>
+      <c r="A263" s="11"/>
+      <c r="B263" s="11"/>
+      <c r="C263" s="11"/>
+      <c r="D263" s="11"/>
     </row>
     <row r="264" ht="12.0" customHeight="1"/>
     <row r="265" ht="12.0" customHeight="1"/>
